--- a/dataset_t6_grouped/results2/G3/G3_T2677_W0056F0003T0006Z000C1N24_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T2677_W0056F0003T0006Z000C1N24_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>1.388478410252104</v>
+        <v>0.2256277416659668</v>
       </c>
       <c r="D2" t="n">
-        <v>4.550930634667272</v>
+        <v>0.7395262281334317</v>
       </c>
       <c r="E2" t="n">
-        <v>6.864725001451726</v>
+        <v>1.115517812735905</v>
       </c>
       <c r="F2" t="n">
-        <v>8.886094148891747</v>
+        <v>1.443990299194909</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>22.95940648395912</v>
+        <v>3.730903553643357</v>
       </c>
       <c r="D3" t="n">
-        <v>23.26900115127184</v>
+        <v>3.781212687081674</v>
       </c>
       <c r="E3" t="n">
-        <v>6.864725001451726</v>
+        <v>1.115517812735905</v>
       </c>
       <c r="F3" t="n">
-        <v>8.886094148891747</v>
+        <v>1.443990299194909</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>13.77618508676299</v>
+        <v>2.238630076598986</v>
       </c>
       <c r="D4" t="n">
-        <v>13.73170054295649</v>
+        <v>2.231401338230429</v>
       </c>
       <c r="E4" t="n">
-        <v>6.864725001451726</v>
+        <v>1.115517812735905</v>
       </c>
       <c r="F4" t="n">
-        <v>8.886094148891747</v>
+        <v>1.443990299194909</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>13.625408999537</v>
+        <v>2.214128962424762</v>
       </c>
       <c r="D5" t="n">
-        <v>17.1144413713313</v>
+        <v>2.781096722841337</v>
       </c>
       <c r="E5" t="n">
-        <v>6.864725001451726</v>
+        <v>1.115517812735905</v>
       </c>
       <c r="F5" t="n">
-        <v>8.886094148891747</v>
+        <v>1.443990299194909</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>9.985473127567202</v>
+        <v>1.62263938322967</v>
       </c>
       <c r="D6" t="n">
-        <v>32.35135236740498</v>
+        <v>5.25709475970331</v>
       </c>
       <c r="E6" t="n">
-        <v>6.864725001451726</v>
+        <v>1.115517812735905</v>
       </c>
       <c r="F6" t="n">
-        <v>8.886094148891747</v>
+        <v>1.443990299194909</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>19.34247072036603</v>
+        <v>3.143151492059481</v>
       </c>
       <c r="D7" t="n">
-        <v>25.16445906432324</v>
+        <v>4.089224597952526</v>
       </c>
       <c r="E7" t="n">
-        <v>6.864725001451726</v>
+        <v>1.115517812735905</v>
       </c>
       <c r="F7" t="n">
-        <v>8.886094148891747</v>
+        <v>1.443990299194909</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
